--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-researchsubject.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-researchsubject.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>StudySubject</t>
@@ -386,7 +386,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ResearchSubject.meta.versionId</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-researchsubject.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-researchsubject.xlsx
@@ -450,7 +450,7 @@
     <t>ResearchSubject.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -488,7 +488,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -546,7 +546,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -715,7 +715,7 @@
     <t>ResearchSubject.study</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -731,7 +731,7 @@
     <t>ResearchSubject.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -765,7 +765,7 @@
     <t>ResearchSubject.consent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Consent)
+    <t xml:space="preserve">Reference(Consent|4.0.1)
 </t>
   </si>
   <si>
@@ -1095,17 +1095,17 @@
   <dimension ref="A1:AN26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="33.62890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.62890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="28.83203125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="28.83203125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="28.6484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1114,26 +1114,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="79.734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="68.359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.0546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="175.1171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="47.87890625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="150.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="41.046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1938,7 +1938,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -4092,12 +4092,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN26">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-researchsubject.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-researchsubject.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
